--- a/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
+++ b/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,6 +427,231 @@
           <t>2025-11-14 22:19:10</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2025-11-18 10:10:49</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2025-11-18 10:13:01</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2025-11-18 10:20:06</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2025-11-18 10:29:14</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2025-11-18 10:32:14</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2025-11-18 10:33:50</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:15:23</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:17:10</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:18:16</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:19:16</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:20:06</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:20:28</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:31:34</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:37:03</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:37:33</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:37:54</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2025-11-18 14:42:13</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:01:43</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:05:06</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:05:21</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:16:01</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:22:07</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:30:55</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:36:56</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:40:43</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>2025-11-18 15:47:00</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>2025-11-18 18:12:54</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>2025-11-18 18:16:28</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>2025-11-18 18:17:19</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>2025-11-18 18:41:17</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>2025-11-18 18:47:19</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>2025-11-18 19:01:51</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>2025-11-18 19:08:40</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>2025-11-19 10:14:33</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>2025-11-19 10:42:33</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>2025-11-19 10:46:24</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>2025-11-19 10:55:33</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>2025-11-19 10:57:51</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:03:08</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:05:14</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:08:45</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:16:44</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:19:27</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:43:40</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>2025-11-19 11:44:34</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -439,6 +664,231 @@
           <t>https://www.comet.com/maurice-filo/rpa-3species-5rxns-mak-ppo/e6fbfb3fc06947aaa577373e72b63637</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/14ce6c367b4743b9b59450da45b5e5ad</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/41ae36163af94543a309b3b99baed035</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/d636576eee5641c49e154f3ca97b5470</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/1157f8e712464035b9d10736328107ed</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/443f93dc40d948d6a24448e9c595c11b</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/c05a295d75f749aabb366be7f5687f13</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/c5d73b30ea7c446d84250ad1a37801fd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/1a60bb458e364a0e8176939960841b36</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/9bddfc8b928a4d4e8172d6065bc4ed38</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/9c5a37045f734e9eb91902692dc8915c</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/a7bb62b2294c4568b43c5620f2408423</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/a159d2f404eb497db823578c23f657a1</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/cae2aaac265846ec857fa70e0501a170</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/62339129685348678503d7b3c7cd6c85</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/05353056fb9140fa83b2dca38c5eb09a</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/2c1b4d94a3464757a87eda8fe9344055</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/3b15d8aa89ae48139478e79fa1974b76</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/6b9ece1161d8446eb83bca39e6502872</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/638812b4ed1045d29b6944b8014cd586</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/9f05de82b5154b018f48b5ffef1be722</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/de147085d82342849d3c48ab38781b8e</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/bc174a43b158421ab5f6a3f61fe207e7</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/f3817e24576549a3b278fdd55a86e916</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/bf68e7a6aad145a6a1b362646c3c801e</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/4d3d072b25a646eb9c9b4dacf50a79ab</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/6a366e73aec5474098bc371afea05502</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/64d8d0d83d7d41bd9c10f44603ac34b7</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/0c3b4001fe5d48d1b473bdf0a1fb1130</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/1d2ef8a8acdb4590b3fb19cbf8656618</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/4b57f76bb39940209f761649093bf2e3</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/2a32eae2c2f94cd0969f43b747114464</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/19790c6cd51140d68cb07b5f28d2de78</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/d86b2ee74fd24999984bde8919b305d5</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/7f6f0f47808346aa8dac2a4b14c6cdb9</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/920afac8ecc74dce91b3f3d6a0268b3e</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/061e4c19773c4c7db7e54e2c4a35a3c1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/bda552eed7e24b91a3b1da5304c1dc91</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/0353a2cf732743b1914dea9f8dd202e0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/477a28ea896341b08f76a776e33d8f3e</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/b3193b80a3004602b4eb5e0f06ffc001</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/9a3e29d2c086425e8cda5a86ae2375ff</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/ecb07f81f57047569d69397beaad0564</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/86e3d64544f048d8ac7eac78ac8ba24a</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/e1594bde8e51444fa10daaa5ce71569e</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/46bf1dbeff904d85a77106dcdddcfc7b</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -449,6 +899,141 @@
       <c r="B3" t="n">
         <v>5</v>
       </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -459,6 +1044,141 @@
       <c r="B4" t="n">
         <v>3</v>
       </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>3</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -469,6 +1189,141 @@
       <c r="B5" t="n">
         <v>2</v>
       </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -479,6 +1334,141 @@
       <c r="B6" t="n">
         <v>1280</v>
       </c>
+      <c r="C6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="K6" t="n">
+        <v>128</v>
+      </c>
+      <c r="L6" t="n">
+        <v>128</v>
+      </c>
+      <c r="M6" t="n">
+        <v>128</v>
+      </c>
+      <c r="N6" t="n">
+        <v>128</v>
+      </c>
+      <c r="O6" t="n">
+        <v>128</v>
+      </c>
+      <c r="P6" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>128</v>
+      </c>
+      <c r="R6" t="n">
+        <v>128</v>
+      </c>
+      <c r="S6" t="n">
+        <v>128</v>
+      </c>
+      <c r="T6" t="n">
+        <v>128</v>
+      </c>
+      <c r="U6" t="n">
+        <v>128</v>
+      </c>
+      <c r="V6" t="n">
+        <v>128</v>
+      </c>
+      <c r="W6" t="n">
+        <v>128</v>
+      </c>
+      <c r="X6" t="n">
+        <v>128</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>128</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>128</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -489,6 +1479,141 @@
       <c r="B7" t="b">
         <v>0</v>
       </c>
+      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
+      <c r="R7" t="b">
+        <v>0</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -499,6 +1624,141 @@
       <c r="B8" t="n">
         <v>0.0003</v>
       </c>
+      <c r="C8" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -509,6 +1769,141 @@
       <c r="B9" t="n">
         <v>300</v>
       </c>
+      <c r="C9" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" t="n">
+        <v>300</v>
+      </c>
+      <c r="E9" t="n">
+        <v>300</v>
+      </c>
+      <c r="F9" t="n">
+        <v>300</v>
+      </c>
+      <c r="G9" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>300</v>
+      </c>
+      <c r="I9" t="n">
+        <v>300</v>
+      </c>
+      <c r="J9" t="n">
+        <v>300</v>
+      </c>
+      <c r="K9" t="n">
+        <v>300</v>
+      </c>
+      <c r="L9" t="n">
+        <v>300</v>
+      </c>
+      <c r="M9" t="n">
+        <v>300</v>
+      </c>
+      <c r="N9" t="n">
+        <v>300</v>
+      </c>
+      <c r="O9" t="n">
+        <v>300</v>
+      </c>
+      <c r="P9" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>300</v>
+      </c>
+      <c r="R9" t="n">
+        <v>300</v>
+      </c>
+      <c r="S9" t="n">
+        <v>300</v>
+      </c>
+      <c r="T9" t="n">
+        <v>300</v>
+      </c>
+      <c r="U9" t="n">
+        <v>300</v>
+      </c>
+      <c r="V9" t="n">
+        <v>300</v>
+      </c>
+      <c r="W9" t="n">
+        <v>300</v>
+      </c>
+      <c r="X9" t="n">
+        <v>300</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -519,6 +1914,141 @@
       <c r="B10" t="n">
         <v>5</v>
       </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -529,6 +2059,141 @@
       <c r="B11" t="n">
         <v>1024</v>
       </c>
+      <c r="C11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -539,6 +2204,141 @@
       <c r="B12" t="n">
         <v>10240</v>
       </c>
+      <c r="C12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="F12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="H12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="V12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="W12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -549,6 +2349,141 @@
       <c r="B13" t="n">
         <v>128</v>
       </c>
+      <c r="C13" t="n">
+        <v>128</v>
+      </c>
+      <c r="D13" t="n">
+        <v>128</v>
+      </c>
+      <c r="E13" t="n">
+        <v>128</v>
+      </c>
+      <c r="F13" t="n">
+        <v>128</v>
+      </c>
+      <c r="G13" t="n">
+        <v>128</v>
+      </c>
+      <c r="H13" t="n">
+        <v>128</v>
+      </c>
+      <c r="I13" t="n">
+        <v>128</v>
+      </c>
+      <c r="J13" t="n">
+        <v>128</v>
+      </c>
+      <c r="K13" t="n">
+        <v>128</v>
+      </c>
+      <c r="L13" t="n">
+        <v>128</v>
+      </c>
+      <c r="M13" t="n">
+        <v>128</v>
+      </c>
+      <c r="N13" t="n">
+        <v>128</v>
+      </c>
+      <c r="O13" t="n">
+        <v>128</v>
+      </c>
+      <c r="P13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>128</v>
+      </c>
+      <c r="R13" t="n">
+        <v>128</v>
+      </c>
+      <c r="S13" t="n">
+        <v>128</v>
+      </c>
+      <c r="T13" t="n">
+        <v>128</v>
+      </c>
+      <c r="U13" t="n">
+        <v>128</v>
+      </c>
+      <c r="V13" t="n">
+        <v>128</v>
+      </c>
+      <c r="W13" t="n">
+        <v>128</v>
+      </c>
+      <c r="X13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -561,6 +2496,231 @@
           <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.05, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.05}</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.05, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.05}</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -573,6 +2733,231 @@
           <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.99, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.99, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.9, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -583,6 +2968,141 @@
       <c r="B16" t="n">
         <v>1</v>
       </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>10</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>10</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10</v>
+      </c>
+      <c r="M16" t="n">
+        <v>10</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10</v>
+      </c>
+      <c r="R16" t="n">
+        <v>10</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10</v>
+      </c>
+      <c r="V16" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" t="n">
+        <v>10</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -593,6 +3113,141 @@
       <c r="B17" t="n">
         <v>20</v>
       </c>
+      <c r="C17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20</v>
+      </c>
+      <c r="J17" t="n">
+        <v>20</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20</v>
+      </c>
+      <c r="O17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>20</v>
+      </c>
+      <c r="R17" t="n">
+        <v>20</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V17" t="n">
+        <v>20</v>
+      </c>
+      <c r="W17" t="n">
+        <v>20</v>
+      </c>
+      <c r="X17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -603,6 +3258,141 @@
       <c r="B18" t="n">
         <v>200</v>
       </c>
+      <c r="C18" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" t="n">
+        <v>200</v>
+      </c>
+      <c r="F18" t="n">
+        <v>200</v>
+      </c>
+      <c r="G18" t="n">
+        <v>200</v>
+      </c>
+      <c r="H18" t="n">
+        <v>200</v>
+      </c>
+      <c r="I18" t="n">
+        <v>200</v>
+      </c>
+      <c r="J18" t="n">
+        <v>200</v>
+      </c>
+      <c r="K18" t="n">
+        <v>200</v>
+      </c>
+      <c r="L18" t="n">
+        <v>200</v>
+      </c>
+      <c r="M18" t="n">
+        <v>200</v>
+      </c>
+      <c r="N18" t="n">
+        <v>200</v>
+      </c>
+      <c r="O18" t="n">
+        <v>200</v>
+      </c>
+      <c r="P18" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>200</v>
+      </c>
+      <c r="R18" t="n">
+        <v>200</v>
+      </c>
+      <c r="S18" t="n">
+        <v>200</v>
+      </c>
+      <c r="T18" t="n">
+        <v>200</v>
+      </c>
+      <c r="U18" t="n">
+        <v>200</v>
+      </c>
+      <c r="V18" t="n">
+        <v>200</v>
+      </c>
+      <c r="W18" t="n">
+        <v>200</v>
+      </c>
+      <c r="X18" t="n">
+        <v>200</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -613,6 +3403,141 @@
       <c r="B19" t="n">
         <v>1000</v>
       </c>
+      <c r="C19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -623,6 +3548,141 @@
       <c r="B20" t="n">
         <v>1</v>
       </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -633,6 +3693,141 @@
       <c r="B21" t="n">
         <v>9</v>
       </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>9</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="n">
+        <v>9</v>
+      </c>
+      <c r="U21" t="n">
+        <v>9</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>9</v>
+      </c>
+      <c r="X21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -645,6 +3840,231 @@
           <t>{'type': 'lognormal_1D'}</t>
         </is>
       </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -653,6 +4073,231 @@
         </is>
       </c>
       <c r="B23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
         </is>

--- a/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
+++ b/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,6 +652,21 @@
           <t>2025-11-19 11:44:34</t>
         </is>
       </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2025-11-19 12:08:19</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>2025-11-19 12:16:37</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>2025-11-19 13:00:00</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -889,6 +904,21 @@
           <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/46bf1dbeff904d85a77106dcdddcfc7b</t>
         </is>
       </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/736487f51917497a8b8d9cbbb416124f</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/127823124f8e4128ac9e67ad49e00ff7</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/74a97873e04f4dd9887be1e132c92f04</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1034,6 +1064,15 @@
       <c r="AU3" t="n">
         <v>5</v>
       </c>
+      <c r="AV3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1179,6 +1218,15 @@
       <c r="AU4" t="n">
         <v>3</v>
       </c>
+      <c r="AV4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1324,6 +1372,15 @@
       <c r="AU5" t="n">
         <v>2</v>
       </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1469,6 +1526,15 @@
       <c r="AU6" t="n">
         <v>1280</v>
       </c>
+      <c r="AV6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1280</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1614,6 +1680,15 @@
       <c r="AU7" t="b">
         <v>0</v>
       </c>
+      <c r="AV7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1759,6 +1834,15 @@
       <c r="AU8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AV8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1904,6 +1988,15 @@
       <c r="AU9" t="n">
         <v>300</v>
       </c>
+      <c r="AV9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2049,6 +2142,15 @@
       <c r="AU10" t="n">
         <v>5</v>
       </c>
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2194,6 +2296,15 @@
       <c r="AU11" t="n">
         <v>1024</v>
       </c>
+      <c r="AV11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2339,6 +2450,15 @@
       <c r="AU12" t="n">
         <v>10240</v>
       </c>
+      <c r="AV12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>10240</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2484,6 +2604,15 @@
       <c r="AU13" t="n">
         <v>128</v>
       </c>
+      <c r="AV13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>128</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2721,6 +2850,21 @@
           <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
         </is>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.02, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.02}</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.005, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.005}</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2958,6 +3102,21 @@
           <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.97, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.97, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3103,6 +3262,15 @@
       <c r="AU16" t="n">
         <v>10</v>
       </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3248,6 +3416,15 @@
       <c r="AU17" t="n">
         <v>20</v>
       </c>
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3393,6 +3570,15 @@
       <c r="AU18" t="n">
         <v>200</v>
       </c>
+      <c r="AV18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3538,6 +3724,15 @@
       <c r="AU19" t="n">
         <v>1000</v>
       </c>
+      <c r="AV19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3683,6 +3878,15 @@
       <c r="AU20" t="n">
         <v>1</v>
       </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3828,6 +4032,15 @@
       <c r="AU21" t="n">
         <v>9</v>
       </c>
+      <c r="AV21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4065,6 +4278,21 @@
           <t>{'type': 'lognormal_1D'}</t>
         </is>
       </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4298,6 +4526,21 @@
         </is>
       </c>
       <c r="AU23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
         <is>
           <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
         </is>

--- a/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
+++ b/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AV28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,6 +652,11 @@
           <t>2025-11-19 11:44:34</t>
         </is>
       </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>2025-11-19 17:34:56</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -889,6 +894,11 @@
           <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/46bf1dbeff904d85a77106dcdddcfc7b</t>
         </is>
       </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/maurice-filo/rpa-3species-5rxns-mak-ppo/910fe18b3e2b4b478d50f8a0de9f634e</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1034,6 +1044,9 @@
       <c r="AU3" t="n">
         <v>5</v>
       </c>
+      <c r="AV3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1179,6 +1192,9 @@
       <c r="AU4" t="n">
         <v>3</v>
       </c>
+      <c r="AV4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1324,6 +1340,9 @@
       <c r="AU5" t="n">
         <v>2</v>
       </c>
+      <c r="AV5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1469,6 +1488,9 @@
       <c r="AU6" t="n">
         <v>1280</v>
       </c>
+      <c r="AV6" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1614,6 +1636,9 @@
       <c r="AU7" t="b">
         <v>0</v>
       </c>
+      <c r="AV7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1759,6 +1784,9 @@
       <c r="AU8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AV8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1904,6 +1932,9 @@
       <c r="AU9" t="n">
         <v>300</v>
       </c>
+      <c r="AV9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2049,6 +2080,9 @@
       <c r="AU10" t="n">
         <v>5</v>
       </c>
+      <c r="AV10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2194,6 +2228,9 @@
       <c r="AU11" t="n">
         <v>1024</v>
       </c>
+      <c r="AV11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2339,6 +2376,9 @@
       <c r="AU12" t="n">
         <v>10240</v>
       </c>
+      <c r="AV12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2484,6 +2524,9 @@
       <c r="AU13" t="n">
         <v>128</v>
       </c>
+      <c r="AV13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2721,6 +2764,11 @@
           <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
         </is>
       </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.001, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.001}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2958,6 +3006,11 @@
           <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.95, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3103,6 +3156,9 @@
       <c r="AU16" t="n">
         <v>10</v>
       </c>
+      <c r="AV16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3248,6 +3304,9 @@
       <c r="AU17" t="n">
         <v>20</v>
       </c>
+      <c r="AV17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3393,6 +3452,9 @@
       <c r="AU18" t="n">
         <v>200</v>
       </c>
+      <c r="AV18" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3538,6 +3600,9 @@
       <c r="AU19" t="n">
         <v>1000</v>
       </c>
+      <c r="AV19" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3683,6 +3748,9 @@
       <c r="AU20" t="n">
         <v>1</v>
       </c>
+      <c r="AV20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3828,6 +3896,9 @@
       <c r="AU21" t="n">
         <v>9</v>
       </c>
+      <c r="AV21" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4065,6 +4136,11 @@
           <t>{'type': 'lognormal_1D'}</t>
         </is>
       </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4298,6 +4374,11 @@
         </is>
       </c>
       <c r="AU23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
         <is>
           <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
         </is>

--- a/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
+++ b/apps_MAK_PPO/RPA_3species_5rxns/RPA_3species_5rxns_MAK_PPO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,6 +667,11 @@
           <t>2025-11-19 13:00:00</t>
         </is>
       </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>2025-11-21 17:17:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -919,6 +924,11 @@
           <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/74a97873e04f4dd9887be1e132c92f04</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>https://www.comet.com/redsnic/rpa-3species-5rxns-mak-ppo/667c984f88a445cb80606ed75c65210c</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1073,6 +1083,9 @@
       <c r="AX3" t="n">
         <v>5</v>
       </c>
+      <c r="AY3" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1227,6 +1240,9 @@
       <c r="AX4" t="n">
         <v>3</v>
       </c>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1381,6 +1397,9 @@
       <c r="AX5" t="n">
         <v>2</v>
       </c>
+      <c r="AY5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1535,6 +1554,9 @@
       <c r="AX6" t="n">
         <v>1280</v>
       </c>
+      <c r="AY6" t="n">
+        <v>1280</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1689,6 +1711,9 @@
       <c r="AX7" t="b">
         <v>0</v>
       </c>
+      <c r="AY7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1843,6 +1868,9 @@
       <c r="AX8" t="n">
         <v>0.0001</v>
       </c>
+      <c r="AY8" t="n">
+        <v>0.0001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1997,6 +2025,9 @@
       <c r="AX9" t="n">
         <v>300</v>
       </c>
+      <c r="AY9" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2151,6 +2182,9 @@
       <c r="AX10" t="n">
         <v>5</v>
       </c>
+      <c r="AY10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2305,6 +2339,9 @@
       <c r="AX11" t="n">
         <v>1024</v>
       </c>
+      <c r="AY11" t="n">
+        <v>1024</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2459,6 +2496,9 @@
       <c r="AX12" t="n">
         <v>10240</v>
       </c>
+      <c r="AY12" t="n">
+        <v>10240</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2613,6 +2653,9 @@
       <c r="AX13" t="n">
         <v>128</v>
       </c>
+      <c r="AY13" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2865,6 +2908,11 @@
           <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
         </is>
       </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>{'entropy_weight': 0.01, 'entropy_update_coefficient': 1, 'entropy_schedule': 1000, 'minimum_entropy_weight': 0.01}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3117,6 +3165,11 @@
           <t>{'risk': 0.97, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
         </is>
       </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>{'risk': 0.97, 'risk_update': 0.0, 'max_risk': 1.0, 'risk_schedule': 1000}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3271,6 +3324,9 @@
       <c r="AX16" t="n">
         <v>10</v>
       </c>
+      <c r="AY16" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3425,6 +3481,9 @@
       <c r="AX17" t="n">
         <v>20</v>
       </c>
+      <c r="AY17" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3579,6 +3638,9 @@
       <c r="AX18" t="n">
         <v>200</v>
       </c>
+      <c r="AY18" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3733,6 +3795,9 @@
       <c r="AX19" t="n">
         <v>1000</v>
       </c>
+      <c r="AY19" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3887,6 +3952,9 @@
       <c r="AX20" t="n">
         <v>1</v>
       </c>
+      <c r="AY20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4041,6 +4109,9 @@
       <c r="AX21" t="n">
         <v>9</v>
       </c>
+      <c r="AY21" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4293,6 +4364,11 @@
           <t>{'type': 'lognormal_1D'}</t>
         </is>
       </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>{'type': 'lognormal_1D'}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4541,6 +4617,11 @@
         </is>
       </c>
       <c r="AX23" t="inlineStr">
+        <is>
+          <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
         <is>
           <t>{'eps': 0.2, 'value_loss_weight': 0.5, 'gamma': 1, 'lam': 0.97, 'update_policy_every': 4}</t>
         </is>
